--- a/artfynd/A 297-2024 artfynd.xlsx
+++ b/artfynd/A 297-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 297-2024 artfynd.xlsx
+++ b/artfynd/A 297-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>119704016</v>
       </c>
       <c r="B5" t="n">
-        <v>91185</v>
+        <v>91203</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 297-2024 artfynd.xlsx
+++ b/artfynd/A 297-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114105184</v>
+        <v>119704016</v>
       </c>
       <c r="B2" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tallstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -802,12 +792,7 @@
         <v>114105370</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,37 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114105064</v>
+        <v>114105184</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,7 +941,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1043,50 +1023,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119704016</v>
+        <v>114105064</v>
       </c>
       <c r="B5" t="n">
-        <v>91203</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1124,17 +1100,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tallstubbe</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1124,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 297-2024 artfynd.xlsx
+++ b/artfynd/A 297-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119704016</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114105370</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114105184</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,8 +1159,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114105064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>